--- a/assets/exam-library/tags.xlsx
+++ b/assets/exam-library/tags.xlsx
@@ -413,11 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,6 +432,11 @@
           <t>tags</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
